--- a/0_assembling/BOM(物料清单)双光融合热成像.xlsx
+++ b/0_assembling/BOM(物料清单)双光融合热成像.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ws\ESP32_Dual_Vision_Thermal\0_assembling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908D5D47-E96B-4B54-879C-12A9905D4CFC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB02FCB9-6288-4F1F-8E86-8182D8FD8531}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32770" yWindow="32770" windowWidth="28800" windowHeight="12380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="148">
   <si>
     <t>ID</t>
   </si>
@@ -224,9 +224,6 @@
   </si>
   <si>
     <t>SOIC-8_L5.3-W5.3-P1.27-LS8.0-BL</t>
-  </si>
-  <si>
-    <t>U11</t>
   </si>
   <si>
     <t>TYPE-C16PIN</t>
@@ -356,19 +353,7 @@
     <t>FFC/FPC连接器0.5-1.0H-4/5/6/8/10/12-40P后翻盖镀金间距0.5mm-淘宝网</t>
   </si>
   <si>
-    <t>FPC1-10P</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>FPC2-6P</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>屏幕排线（选0.5-1.0H-10P 后翻盖镀金）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>屏幕排线（选0.5-1.0H-6P 后翻盖镀金）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -419,9 +404,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>包邮 轻触开关 侧按键 2*4*3.5/3*6*3.5 小侧按/大侧按 贴片 微动-淘宝网 (taobao.com)</t>
-  </si>
-  <si>
     <t>日本ALPS SSAJ120100 小薄型拨动开关5脚2档 滑动推进开关 贴片-淘宝网 (taobao.com)</t>
   </si>
   <si>
@@ -437,9 +419,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>全新原装 ESP32-D0WD-V3 QFN-48 双核Wi-Fi&amp;蓝牙MCU无线收发芯片-淘宝网</t>
-  </si>
-  <si>
     <t>HEIMANN-5.0（探头二选一）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -458,21 +437,12 @@
   <si>
     <t>W25Q32JVSSIQ</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>原装正品 贴片 W25Q32JVSSIQ SOIC-8 IC FLASH闪存芯片 32MBIT-淘宝网</t>
-  </si>
-  <si>
-    <t>USB Type-C 16P母座卧贴板上四脚插高清传输接口插座USB连接器-淘宝网</t>
   </si>
   <si>
     <t>https://item.taobao.com/item.htm?spm=a1z0d.6639537%2F202410.item.d615686264044.19617484TONjiv&amp;id=615686264044&amp;from=cart&amp;skuId=5305137541548&amp;pisk=gdvjjNiolr4fQQ6TfsmPVXeLchB610kECls9xhe4XtBA5Ot6v1eZit51CUQy3Z-VHN66fHC97N-4mQYev-JqiOy1nOXt82kELmxcIOI7do8To7IVYASTMSBceE7-O8DELnx70ine2vJ28I6fc5e9WsC8eGQRDiFYM06RfMWTH1eYwzQlyOEABRF8wMjLB5LOXTeRAiFOXGQ92gIhyNBOBFK-VG7RWb4QPGlfXniAQD023lI6DawTBKHGGwsu_Rw1FiCXBnQ74uJ5cs_dZdMf7KLyXKJcZbPlI3RB5CLiT7XXXIBAYnDbF9KvadsyQcP1kEvW2K57D-CX6G1dB_ZTB36vw6pRpvU5qQK26KYbfRID3p51-_iTI1WJL6dpllmH2tI9S6vZ--bvXHvHT9MzM9KW6eO14ryFRiZ71u13Cg_EV0NgsLzL1hFXMg4FMgjxL0i7P5fAqgQKV0NiJsIlcMnSVrqd.</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>原装正品 0603贴片电阻 680K 标字684 1/10W 精度5% （200只）-淘宝网 (taobao.com)</t>
-  </si>
-  <si>
     <t>https://oshwhub.com/umekoko/esp32-shuang-guang-rong-ge-re-cheng-xiang-yi</t>
   </si>
   <si>
@@ -508,6 +478,46 @@
   </si>
   <si>
     <t>固定螺丝 M2*8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?spm=tbpc.boughtlist.suborder_itemtitle.1.48532e8d5pOfKX&amp;id=740684741262&amp;mi_id=00003H5VHBSXfy2G2Bu8x1tffMKAFsDOL1eUYOR3FCrkgZA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?abbucket=18&amp;id=739112411448&amp;mi_id=0000PBJsLvMIztkxFB6PA2RMHILraPhRWEAD9ZH_MPLna_M&amp;ns=1&amp;skuId=5268164442138&amp;spm=a21n57.1.hoverItem.1&amp;utparam=%7B%22aplus_abtest%22%3A%224c807a4861ff1de841e85707019c1d96%22%7D&amp;xxc=taobaoSearch</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?abbucket=18&amp;id=711754119886&amp;mi_id=0000m9qbahef8Kja8bcSxbJJtX_lOBq3tVGUgtQmZoeMyb0&amp;ns=1&amp;priceTId=214781c617729502879301418e18c7&amp;skuId=4983175856328&amp;spm=a21n57.1.hoverItem.1&amp;utparam=%7B%22aplus_abtest%22%3A%2245fe2c886ec4312ae70e7e6d1c98020c%22%7D&amp;xxc=taobaoSearch</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FPC-24P</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FPC-10P</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>屏幕触摸排线【暂时未使用】（选0.5-1.0H-6P 后翻盖镀金）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FPC-6P</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?id=735834856054&amp;pisk=gJa8_GNyTtXolYU-i7SDx0ddMD1DJiVzg8P6-vDkA-eYp5duqDDnA2eaBDTh44mKJ-M0rYVoPXiQKRZoFuDHJye4eUYnPJbKd5rVTYcurBhQc8L3q7DuDB3zouYnETuLOR0dIObGS7Pru26GIzzTeeusNvMBKYOXl2cLm7tk17Pr8vODdGqbaBHu6ZOIOv1xlXhSd2iSNq9j3XxSdJMScKGt_2gQdYgjcXhWRUMINI1x1X-WdYMBGEGtO3TQd21YGxlIRbwIRv-F2xdSMeENhUWsrtOX5Faxw0Hp-YTKtr8i0Agr3e6_jbpZC7MvReMup7E7M7XJ7S0zGRhgEZT8BSVgzmzdBanzl5Uq2yRp0SmZeqMzqTLqw8VLWma5tCD7uWaZDVIeIxzUGlmZ5LtS64H-fzwDO1gSAXgSUuXJubeu9PnbP6xigkw4J4017LM3m5UK9yWFkRF0szo4JOQf4czgWNwkIAhHVsCvYHoSgcl0djZFXZDKMAf-wH-EAjlxIsCvYHoSgjHGwLKeYDGV.%5DuQoTrNOmxDHrpTLN8wmnvjBAeF7FoDmKF4BJ7Zw1..&amp;skuId=5084031056234&amp;spm=tbpc.boughtlist.suborder_itemtitle.1.39dd2e8d3P2TeZ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?abbucket=18&amp;id=739548859339&amp;mi_id=0000TfLo-alRxWnrYWt3xXq_e0HBqb5tf9MDXdPbk8iGxv0&amp;ns=1&amp;priceTId=214781c617729504198103237e18c7&amp;skuId=5274097539204&amp;spm=a21n57.1.hoverItem.8&amp;utparam=%7B%22aplus_abtest%22%3A%22d1925f573d79f5ccbaa5108f93f1e9ea%22%7D&amp;xxc=taobaoSearch</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?id=525843631800&amp;pisk=f2qZM_6J2GIZl656PfoV40HaaTitS0CSjoGjn-2mCfci1oN4nxMxIxxmopmnnXtfBc_x0SlUMfgsjftq0-PYGqqjGoJTY7-Xf1QTnnojm_15VgwOBmncNnIdVrpthxMMSIGDtpAmg8B5VgwTLY-rS9S75ul6g4MmmVcgKMcKhIx0iVcntXHxnCmms9ynOIqf_asiW_Vntyb0ST-P9AGem3J-QV0O2XxDlkDaLb2iknx0YAuaYL4V2ig_o838fJs2vcwz-DDzqsLqGlw7cDmVYQcQX8a-ylBkFXq_nuh_j6tsslUUPqzOaUFrbSuuj2JDmJo45Dk3qtT-Okl_iluhF3ujxugojy_d1qiZUSqT_K-0Zg8XMvVWdoUwiEuipvl5L9lq-zfajrZQOELx8wHENTBJkE3GQvl5emYvk2vrLb6kh&amp;spm=a1z10.3-c-s.w4002-24706531953.11.22dd6a4bifxpAD</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -515,7 +525,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -567,7 +577,16 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="8"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF18191C"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -604,7 +623,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -626,7 +645,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1121,7 +1143,7 @@
   <dimension ref="A1:F43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="38.6328125" customWidth="1"/>
+    <col min="2" max="2" width="54.26953125" customWidth="1"/>
     <col min="3" max="3" width="15.7265625" customWidth="1"/>
     <col min="4" max="4" width="38.81640625" customWidth="1"/>
     <col min="5" max="5" width="10.453125" customWidth="1"/>
@@ -1136,16 +1158,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1165,7 +1187,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1185,7 +1207,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1196,7 +1218,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
@@ -1205,7 +1227,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1225,7 +1247,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1236,7 +1258,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
@@ -1245,7 +1267,7 @@
         <v>3</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1256,7 +1278,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
@@ -1265,7 +1287,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1285,7 +1307,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1305,7 +1327,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1313,7 +1335,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
         <v>21</v>
@@ -1325,7 +1347,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1333,7 +1355,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
         <v>23</v>
@@ -1345,7 +1367,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1353,7 +1375,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
         <v>25</v>
@@ -1365,7 +1387,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1373,7 +1395,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s">
         <v>26</v>
@@ -1385,7 +1407,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1405,7 +1427,7 @@
         <v>4</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1413,7 +1435,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C15" t="s">
         <v>30</v>
@@ -1425,7 +1447,7 @@
         <v>2</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1445,7 +1467,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1465,7 +1487,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1473,10 +1495,10 @@
         <v>19</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="D18" t="s">
         <v>36</v>
@@ -1485,7 +1507,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1493,10 +1515,10 @@
         <v>20</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="D19" t="s">
         <v>37</v>
@@ -1505,7 +1527,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1525,7 +1547,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1545,7 +1567,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1565,7 +1587,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1585,7 +1607,7 @@
         <v>3</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1605,7 +1627,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1625,7 +1647,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1645,7 +1667,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1665,7 +1687,7 @@
         <v>2</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1673,7 +1695,7 @@
         <v>29</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C28" t="s">
         <v>56</v>
@@ -1685,7 +1707,7 @@
         <v>2</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="16.5">
@@ -1693,7 +1715,7 @@
         <v>31</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C29" t="s">
         <v>57</v>
@@ -1705,7 +1727,7 @@
         <v>2</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1725,7 +1747,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:6" s="4" customFormat="1">
@@ -1733,19 +1755,19 @@
         <v>33</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>62</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E31" s="4">
         <v>1</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" spans="1:6" s="4" customFormat="1">
@@ -1753,19 +1775,19 @@
         <v>34</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>63</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E32" s="4">
         <v>1</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1773,7 +1795,7 @@
         <v>35</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
         <v>64</v>
@@ -1785,7 +1807,7 @@
         <v>1</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1793,7 +1815,7 @@
         <v>36</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C34" t="s">
         <v>66</v>
@@ -1805,7 +1827,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1813,19 +1835,19 @@
         <v>37</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C35" t="s">
-        <v>68</v>
+        <v>143</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
-      <c r="F35" s="2" t="s">
-        <v>105</v>
+      <c r="F35" s="7" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1833,19 +1855,19 @@
         <v>38</v>
       </c>
       <c r="B36" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" t="s">
         <v>69</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>70</v>
       </c>
-      <c r="D36" t="s">
-        <v>71</v>
-      </c>
       <c r="E36">
         <v>1</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1853,19 +1875,19 @@
         <v>39</v>
       </c>
       <c r="B37" t="s">
+        <v>71</v>
+      </c>
+      <c r="C37" t="s">
         <v>72</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>73</v>
       </c>
-      <c r="D37" t="s">
-        <v>74</v>
-      </c>
       <c r="E37">
         <v>1</v>
       </c>
-      <c r="F37" s="2" t="s">
-        <v>134</v>
+      <c r="F37" s="7" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1873,10 +1895,10 @@
         <v>40</v>
       </c>
       <c r="B38" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" t="s">
         <v>75</v>
-      </c>
-      <c r="C38" t="s">
-        <v>76</v>
       </c>
       <c r="D38" t="s">
         <v>8</v>
@@ -1885,44 +1907,44 @@
         <v>1</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" t="s">
-        <v>77</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>136</v>
+        <v>76</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="B40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="1" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="F41" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="B42" s="1" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="F42" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="B43" s="1" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="F43" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1955,11 +1977,16 @@
     <hyperlink ref="F16" r:id="rId25" display="https://item.taobao.com/item.htm?spm=a1z0d.6639537/202406.item.d522577340017.55217484l4jjji&amp;id=522577340017&amp;from=cart&amp;pisk=fpBtgENUBy4iWJVcCGNHnORckKq3DOINvNSSnEYiGwQdlZKmniTDHZQAkFAb7dXAJZ_vmxjfnn6vQ9finF4wHi_kHz4uE8jNbpJbrzAZE2hDFn-jhqD6OB_MR7HUE8jNvcx_qMwu0zeURUtXhCOXOHTeDAi61Z9IO3YICnM6c2Zp0eTXhIOXdJt2XhG6fIM6J5LZhUHAGtT1fOGxEfhOpHa2PGEqGe5HXoTlXeUWT9ttUUs6JxMX7MfAjMIgWYSHQT7JqN2IBaIPLwKCP-Up3w5flnQQUqvNZNWy9MPSdMJ9kQTCFVG62dL9NOOQeuI9G6BpIOaqaMjp5QphtWzMidQOaUR_Ty7AvFbfBBgT-EflxOOdPyDduICPmnQTBA_549XleGBmrUKm1kEKgjR6xbNxK2xzGj2XvUqMjjl2OLkm6tbSGjgq4HLujVcqgB9P." xr:uid="{00000000-0004-0000-0000-000018000000}"/>
     <hyperlink ref="F15" r:id="rId26" display="https://item.taobao.com/item.htm?id=523821513172&amp;pisk=fFGiMD4PVAysd1SgPpV6dpwwFhJpXGNbfmCYDSE2LkrC6mFTMWrUkrI4usyaYv0SmlLXC5H3mDo3b1L6C-rmfknAMVhmds0SlfL_MFNs5SN223d-mVg_GUnIXic0Tkz7SIBa3Szgt1Vv23dJi957vnx-WpqkQOU0YP5ags83LPUzgPrNgeqUozZV_mPqOq817oxiZFV3qg8AxrNdW7Zr7lutWXPG2u0axsf0jP2MBVrhgsln3LDaRlJ5JoNTf4aicQ1__-DrtRMBA9rxdDVarb-fnohtyjFEAnXY4Ahsi8hMqTNi1qkYKvsNQzVgj8laKZ5a9-knt5hwcTgK-lyu9vpBX-FijYZ7QptIm2qt0f2FjgzRLTlfVsaekXWfhRzQ-u3f_Hgixf1LweYheqwaRzZJ-eXfURzQPuYH-Th3QyaPL&amp;spm=a1z10.3-c-s.w4002-24706531953.11.29206a4b3x1sGm" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
     <hyperlink ref="F14" r:id="rId27" display="https://item.taobao.com/item.htm?id=633439444695&amp;pisk=fzSEwz2xDkEEqFPIlB-z05Wky0-pRnFXtgOWETXkdBAnRHioE616-w17pQJlU1L5dWBkE35GNJdCEWCP4CXRRJL79Y7N9tYCaTepEQflaQ_Q5o6dp3KuG3rbc9Ktx1AdaeAHSAX9LQm3T9vSy3KuG7JuIG-226yZ74JySRJWepAlZBXMICpr-XfktFcMeLKkZXsBWr0upeNcsCbi2_CdIbS9_0mqHp8hoodiqzjMLORfKznoqGJe8GuUQ4gvRaXvkM6_4cKC3NxM3iV-zQsChgtM4llD1MBfkEILnxOGATjvOMVsABjd7ZTPJSuAgH5yoMYZE0Xw4wtwIi2SkCswO_jeS-i2PhjXoHb_WWTWYK5lv6krqsjy4bpGGAsR8b0y-dpwGRywaFb0Tztqh60-yFz9QIwYH43J-dvwG-emy4LNudRbnG1..&amp;spm=a1z10.3-c-s.w4002-24706531953.23.3b526a4b1U9SkO" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="F29" r:id="rId28" display="https://item.taobao.com/item.htm?spm=a1z0d.6639537/202406.item.d522577340017.55217484l4jjji&amp;id=522577340017&amp;from=cart&amp;pisk=fpBtgENUBy4iWJVcCGNHnORckKq3DOINvNSSnEYiGwQdlZKmniTDHZQAkFAb7dXAJZ_vmxjfnn6vQ9finF4wHi_kHz4uE8jNbpJbrzAZE2hDFn-jhqD6OB_MR7HUE8jNvcx_qMwu0zeURUtXhCOXOHTeDAi61Z9IO3YICnM6c2Zp0eTXhIOXdJt2XhG6fIM6J5LZhUHAGtT1fOGxEfhOpHa2PGEqGe5HXoTlXeUWT9ttUUs6JxMX7MfAjMIgWYSHQT7JqN2IBaIPLwKCP-Up3w5flnQQUqvNZNWy9MPSdMJ9kQTCFVG62dL9NOOQeuI9G6BpIOaqaMjp5QphtWzMidQOaUR_Ty7AvFbfBBgT-EflxOOdPyDduICPmnQTBA_549XleGBmrUKm1kEKgjR6xbNxK2xzGj2XvUqMjjl2OLkm6tbSGjgq4HLujVcqgB9P." xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="F29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
     <hyperlink ref="F30" r:id="rId29" display="https://item.taobao.com/item.htm?id=523821513172&amp;pisk=fFGiMD4PVAysd1SgPpV6dpwwFhJpXGNbfmCYDSE2LkrC6mFTMWrUkrI4usyaYv0SmlLXC5H3mDo3b1L6C-rmfknAMVhmds0SlfL_MFNs5SN223d-mVg_GUnIXic0Tkz7SIBa3Szgt1Vv23dJi957vnx-WpqkQOU0YP5ags83LPUzgPrNgeqUozZV_mPqOq817oxiZFV3qg8AxrNdW7Zr7lutWXPG2u0axsf0jP2MBVrhgsln3LDaRlJ5JoNTf4aicQ1__-DrtRMBA9rxdDVarb-fnohtyjFEAnXY4Ahsi8hMqTNi1qkYKvsNQzVgj8laKZ5a9-knt5hwcTgK-lyu9vpBX-FijYZ7QptIm2qt0f2FjgzRLTlfVsaekXWfhRzQ-u3f_Hgixf1LweYheqwaRzZJ-eXfURzQPuYH-Th3QyaPL&amp;spm=a1z10.3-c-s.w4002-24706531953.11.29206a4b3x1sGm" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="F33" r:id="rId30" display="https://item.taobao.com/item.htm?id=633439444695&amp;pisk=fzSEwz2xDkEEqFPIlB-z05Wky0-pRnFXtgOWETXkdBAnRHioE616-w17pQJlU1L5dWBkE35GNJdCEWCP4CXRRJL79Y7N9tYCaTepEQflaQ_Q5o6dp3KuG3rbc9Ktx1AdaeAHSAX9LQm3T9vSy3KuG7JuIG-226yZ74JySRJWepAlZBXMICpr-XfktFcMeLKkZXsBWr0upeNcsCbi2_CdIbS9_0mqHp8hoodiqzjMLORfKznoqGJe8GuUQ4gvRaXvkM6_4cKC3NxM3iV-zQsChgtM4llD1MBfkEILnxOGATjvOMVsABjd7ZTPJSuAgH5yoMYZE0Xw4wtwIi2SkCswO_jeS-i2PhjXoHb_WWTWYK5lv6krqsjy4bpGGAsR8b0y-dpwGRywaFb0Tztqh60-yFz9QIwYH43J-dvwG-emy4LNudRbnG1..&amp;spm=a1z10.3-c-s.w4002-24706531953.23.3b526a4b1U9SkO" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="F31" r:id="rId30" display="https://item.taobao.com/item.htm?abbucket=18&amp;id=593529980153&amp;mi_id=0000_fEiqWgG0TOeUFOniVyDdJYmWyzqsGN5yUcxPPm3K6E&amp;ns=1&amp;priceTId=215043dd17721968011585394e191a&amp;spm=a21n57.1.hoverItem.2&amp;utparam=%7B%22aplus_abtest%22%3A%22bd7363f5712bca97d21b735e52a690f8%22%7D&amp;xxc=taobaoSearch" xr:uid="{1DAD49E8-3128-4692-849F-59A4EFA09B36}"/>
+    <hyperlink ref="F32" r:id="rId31" display="https://item.taobao.com/item.htm?abbucket=18&amp;id=733065282196&amp;mi_id=00004_KVSGTEv6DXz6xbtdfms4DUOo1f--258oLeFh2Koo4&amp;ns=1&amp;priceTId=213e077617721970377426676e0d60&amp;spm=a21n57.1.hoverItem.2&amp;utparam=%7B%22aplus_abtest%22%3A%22a0ab5ac77c0005f3eee82e5e7d5d3d30%22%7D&amp;xxc=taobaoSearch" xr:uid="{1374BDFB-3BEC-49CA-8F02-96AA10CA1E4D}"/>
+    <hyperlink ref="F33" r:id="rId32" xr:uid="{647C8286-659C-4418-8402-954097D1F898}"/>
+    <hyperlink ref="F34" r:id="rId33" display="https://item.taobao.com/item.htm?abbucket=18&amp;id=711754119886&amp;mi_id=0000m9qbahef8Kja8bcSxbJJtX_lOBq3tVGUgtQmZoeMyb0&amp;ns=1&amp;priceTId=214781c617729502879301418e18c7&amp;skuId=4983175856328&amp;spm=a21n57.1.hoverItem.1&amp;utparam=%7B%22aplus_abtest%22%3A%2245fe2c886ec4312ae70e7e6d1c98020c%22%7D&amp;xxc=taobaoSearch" xr:uid="{695E752D-F08C-45A0-8082-59FEA77EB244}"/>
+    <hyperlink ref="F36" r:id="rId34" display="https://item.taobao.com/item.htm?abbucket=18&amp;id=739548859339&amp;mi_id=0000TfLo-alRxWnrYWt3xXq_e0HBqb5tf9MDXdPbk8iGxv0&amp;ns=1&amp;priceTId=214781c617729504198103237e18c7&amp;skuId=5274097539204&amp;spm=a21n57.1.hoverItem.8&amp;utparam=%7B%22aplus_abtest%22%3A%22d1925f573d79f5ccbaa5108f93f1e9ea%22%7D&amp;xxc=taobaoSearch" xr:uid="{DDB3B28A-9D85-4599-A5EB-5074DBDABB4E}"/>
+    <hyperlink ref="F38" r:id="rId35" display="https://item.taobao.com/item.htm?id=525843631800&amp;pisk=f2qZM_6J2GIZl656PfoV40HaaTitS0CSjoGjn-2mCfci1oN4nxMxIxxmopmnnXtfBc_x0SlUMfgsjftq0-PYGqqjGoJTY7-Xf1QTnnojm_15VgwOBmncNnIdVrpthxMMSIGDtpAmg8B5VgwTLY-rS9S75ul6g4MmmVcgKMcKhIx0iVcntXHxnCmms9ynOIqf_asiW_Vntyb0ST-P9AGem3J-QV0O2XxDlkDaLb2iknx0YAuaYL4V2ig_o838fJs2vcwz-DDzqsLqGlw7cDmVYQcQX8a-ylBkFXq_nuh_j6tsslUUPqzOaUFrbSuuj2JDmJo45Dk3qtT-Okl_iluhF3ujxugojy_d1qiZUSqT_K-0Zg8XMvVWdoUwiEuipvl5L9lq-zfajrZQOELx8wHENTBJkE3GQvl5emYvk2vrLb6kh&amp;spm=a1z10.3-c-s.w4002-24706531953.11.22dd6a4bifxpAD" xr:uid="{72177BAE-8E43-468B-92C0-35D8C37C9229}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId31"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId36"/>
 </worksheet>
 </file>